--- a/table/Datas/#Queue.xlsx
+++ b/table/Datas/#Queue.xlsx
@@ -672,7 +672,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8</t>
+          <t>1,2,3,4,5,6,7,8,9</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -720,7 +720,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8</t>
+          <t>1,2,3,4,5,6,7,8,9</t>
         </is>
       </c>
       <c r="L6" t="n">

--- a/table/Datas/#Queue.xlsx
+++ b/table/Datas/#Queue.xlsx
@@ -720,7 +720,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9</t>
+          <t>1,2,3,4,5,6,7,8</t>
         </is>
       </c>
       <c r="L6" t="n">

--- a/table/Datas/#Queue.xlsx
+++ b/table/Datas/#Queue.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,16 @@
           <t>ticket_ttl_seconds</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>lobby_target_players</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>lobby_min_players</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -549,6 +559,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -566,6 +586,16 @@
           <t>m</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -631,6 +661,16 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>ticket_ttl_seconds</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>lobby_target_players</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>lobby_min_players</t>
         </is>
       </c>
     </row>
@@ -681,6 +721,12 @@
       <c r="M5" t="n">
         <v>600</v>
       </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -720,7 +766,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8</t>
+          <t>5,6,7,8</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -728,6 +774,12 @@
       </c>
       <c r="M6" t="n">
         <v>600</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#Queue.xlsx
+++ b/table/Datas/#Queue.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>친선전</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -739,7 +739,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>랭킹전</t>
+          <t>랭크</t>
         </is>
       </c>
       <c r="E6" t="n">

--- a/table/Datas/#Queue.xlsx
+++ b/table/Datas/#Queue.xlsx
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="F6" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G6" t="n">
         <v>10</v>

--- a/table/Datas/#Queue.xlsx
+++ b/table/Datas/#Queue.xlsx
@@ -712,7 +712,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9</t>
+          <t>2,3,4,5,6,7,8,9</t>
         </is>
       </c>
       <c r="L5" t="n">

--- a/table/Datas/#Queue.xlsx
+++ b/table/Datas/#Queue.xlsx
@@ -766,7 +766,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>5,6,7,8</t>
+          <t>5,6,8</t>
         </is>
       </c>
       <c r="L6" t="n">

--- a/table/Datas/#Queue.xlsx
+++ b/table/Datas/#Queue.xlsx
@@ -712,7 +712,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2,3,4,5,6,7,8,9</t>
+          <t>2,3,4,5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="L5" t="n">

--- a/table/Datas/#Queue.xlsx
+++ b/table/Datas/#Queue.xlsx
@@ -712,7 +712,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2,3,4,5,6,7,8,9,10</t>
+          <t>2,3,4,5,6,7,8,9,10,11</t>
         </is>
       </c>
       <c r="L5" t="n">
